--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.67059704707229</v>
+        <v>2.871472020149247</v>
       </c>
       <c r="D2" t="n">
-        <v>9.755310151884913</v>
+        <v>1.585237899681298</v>
       </c>
       <c r="E2" t="n">
-        <v>12.7266512784821</v>
+        <v>2.068080832753342</v>
       </c>
       <c r="F2" t="n">
-        <v>7.192451944496309</v>
+        <v>1.16877344098065</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.59661047149362</v>
+        <v>3.021949201617713</v>
       </c>
       <c r="D3" t="n">
-        <v>18.69640488317355</v>
+        <v>3.038165793515703</v>
       </c>
       <c r="E3" t="n">
-        <v>12.7266512784821</v>
+        <v>2.068080832753342</v>
       </c>
       <c r="F3" t="n">
-        <v>7.192451944496309</v>
+        <v>1.16877344098065</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.44865033877672</v>
+        <v>3.160405680051217</v>
       </c>
       <c r="D4" t="n">
-        <v>30.88989883717276</v>
+        <v>5.019608561040574</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7266512784821</v>
+        <v>2.068080832753342</v>
       </c>
       <c r="F4" t="n">
-        <v>7.192451944496309</v>
+        <v>1.16877344098065</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.05939221461203</v>
+        <v>5.697151234874456</v>
       </c>
       <c r="D5" t="n">
-        <v>31.22663731189377</v>
+        <v>5.074328563182737</v>
       </c>
       <c r="E5" t="n">
-        <v>12.7266512784821</v>
+        <v>2.068080832753342</v>
       </c>
       <c r="F5" t="n">
-        <v>7.192451944496309</v>
+        <v>1.16877344098065</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.59802419126948</v>
+        <v>5.784678931081291</v>
       </c>
       <c r="D6" t="n">
-        <v>22.0615622051423</v>
+        <v>3.585003858335624</v>
       </c>
       <c r="E6" t="n">
-        <v>12.7266512784821</v>
+        <v>2.068080832753342</v>
       </c>
       <c r="F6" t="n">
-        <v>7.192451944496309</v>
+        <v>1.16877344098065</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.81390756699458</v>
+        <v>8.582259979636619</v>
       </c>
       <c r="D7" t="n">
-        <v>25.32312722681381</v>
+        <v>4.115008174357245</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7266512784821</v>
+        <v>2.068080832753342</v>
       </c>
       <c r="F7" t="n">
-        <v>7.192451944496309</v>
+        <v>1.16877344098065</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.57107608030871</v>
+        <v>2.367799863050165</v>
       </c>
       <c r="D8" t="n">
-        <v>14.67824737117917</v>
+        <v>2.385215197816616</v>
       </c>
       <c r="E8" t="n">
-        <v>12.7266512784821</v>
+        <v>2.068080832753342</v>
       </c>
       <c r="F8" t="n">
-        <v>7.192451944496309</v>
+        <v>1.16877344098065</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.61204871897051</v>
+        <v>6.436957916832709</v>
       </c>
       <c r="D9" t="n">
-        <v>16.51767947907517</v>
+        <v>2.684122915349715</v>
       </c>
       <c r="E9" t="n">
-        <v>12.7266512784821</v>
+        <v>2.068080832753342</v>
       </c>
       <c r="F9" t="n">
-        <v>7.192451944496309</v>
+        <v>1.16877344098065</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
